--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
@@ -3,7 +3,7 @@
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:workbookProtection workbookPassword="C258" lockStructure="1"/>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R33761e5526ad486f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4b8adb4e68c248e8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
@@ -3,7 +3,7 @@
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:workbookProtection workbookPassword="C258" lockStructure="1"/>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4b8adb4e68c248e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R350f087c194c4342"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
@@ -3,7 +3,7 @@
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:workbookProtection workbookPassword="C258" lockStructure="1"/>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R350f087c194c4342"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdcf581b164794a34"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
@@ -3,7 +3,7 @@
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:workbookProtection workbookPassword="C258" lockStructure="1"/>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdcf581b164794a34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc39c4cd132534153"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
@@ -3,7 +3,7 @@
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:workbookProtection workbookPassword="C258" lockStructure="1"/>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc39c4cd132534153"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R02de54b7a99d4fea"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/WorkbookProtection/output.xlsx
@@ -3,7 +3,7 @@
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:workbookProtection workbookPassword="C258" lockStructure="1"/>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R02de54b7a99d4fea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R40584ed630fb4fe9"/>
   </x:sheets>
 </x:workbook>
 </file>
